--- a/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
@@ -479,7 +479,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>1459</v>
+        <v>1447</v>
       </c>
       <c r="G2" t="n">
         <v>3261.86</v>
@@ -535,7 +535,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1621</v>
+        <v>1612</v>
       </c>
       <c r="G6" t="n">
         <v>1372.03</v>
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G14" t="n">
-        <v>5931.36</v>
+        <v>11862.72</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -871,7 +871,7 @@
         <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>3342</v>
+        <v>3329</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>28</v>
       </c>
       <c r="F17" t="n">
-        <v>5660</v>
+        <v>5577</v>
       </c>
       <c r="G17" t="n">
         <v>1185.59</v>
@@ -927,7 +927,7 @@
         <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>3542</v>
+        <v>3533</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -955,7 +955,7 @@
         <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>3425</v>
+        <v>3401</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>5203</v>
+        <v>5071</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>1002</v>
+        <v>988</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>3002</v>
+        <v>2987</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>2430</v>
+        <v>2411</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1263,13 +1263,13 @@
         <v>27</v>
       </c>
       <c r="F30" t="n">
-        <v>1850</v>
+        <v>1836</v>
       </c>
       <c r="G30" t="n">
-        <v>6480.52</v>
+        <v>12792.38</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1291,7 +1291,7 @@
         <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>1421</v>
+        <v>1399</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>134</v>
       </c>
       <c r="F32" t="n">
-        <v>8333</v>
+        <v>8291</v>
       </c>
       <c r="G32" t="n">
-        <v>5125.43</v>
+        <v>2244.92</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1347,7 +1347,7 @@
         <v>45</v>
       </c>
       <c r="F33" t="n">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>14</v>
       </c>
       <c r="F35" t="n">
-        <v>3758</v>
+        <v>3638</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>1148</v>
+        <v>1118</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="G38" t="n">
         <v>490.68</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1543,7 +1543,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1627,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>1288</v>
+        <v>1268</v>
       </c>
       <c r="G43" t="n">
         <v>422.88</v>
@@ -1711,7 +1711,7 @@
         <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="G46" t="n">
         <v>1355.08</v>
@@ -1739,7 +1739,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>1127</v>
+        <v>1113</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>29</v>
       </c>
       <c r="F48" t="n">
-        <v>4446</v>
+        <v>4431</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>46</v>
       </c>
       <c r="F51" t="n">
-        <v>7530</v>
+        <v>7488</v>
       </c>
       <c r="G51" t="n">
         <v>4066.95</v>
@@ -1879,7 +1879,7 @@
         <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>6253</v>
+        <v>6229</v>
       </c>
       <c r="G52" t="n">
         <v>4066.95</v>
@@ -1907,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="F53" t="n">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="G53" t="n">
         <v>4066.95</v>
@@ -1935,7 +1935,7 @@
         <v>129</v>
       </c>
       <c r="F54" t="n">
-        <v>15100</v>
+        <v>14930</v>
       </c>
       <c r="G54" t="n">
         <v>8133.9</v>
@@ -1963,7 +1963,7 @@
         <v>48</v>
       </c>
       <c r="F55" t="n">
-        <v>4749</v>
+        <v>4737</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
         <v>13</v>
       </c>
       <c r="F56" t="n">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2019,7 +2019,7 @@
         <v>95</v>
       </c>
       <c r="F57" t="n">
-        <v>10654</v>
+        <v>10392</v>
       </c>
       <c r="G57" t="n">
         <v>4066.95</v>
@@ -2075,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2131,7 +2131,7 @@
         <v>45</v>
       </c>
       <c r="F61" t="n">
-        <v>6197</v>
+        <v>6151</v>
       </c>
       <c r="G61" t="n">
         <v>6438.98</v>
@@ -2159,7 +2159,7 @@
         <v>19</v>
       </c>
       <c r="F62" t="n">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>44</v>
       </c>
       <c r="F63" t="n">
-        <v>6347</v>
+        <v>6305</v>
       </c>
       <c r="G63" t="n">
         <v>1397.46</v>
@@ -2215,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="F64" t="n">
-        <v>3636</v>
+        <v>3599</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>5</v>
       </c>
       <c r="F65" t="n">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>2745</v>
+        <v>2714</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="F68" t="n">
-        <v>2162</v>
+        <v>2155</v>
       </c>
       <c r="G68" t="n">
         <v>4405.93</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2383,13 +2383,13 @@
         <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>4405.93</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2439,7 +2439,7 @@
         <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>1493</v>
+        <v>1481</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>6280</v>
+        <v>6256</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="F76" t="n">
-        <v>2220</v>
+        <v>2204</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="G77" t="n">
         <v>1007.63</v>
@@ -2719,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="F83" t="n">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="F84" t="n">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>147</v>
       </c>
       <c r="F85" t="n">
-        <v>14847</v>
+        <v>14635</v>
       </c>
       <c r="G85" t="n">
         <v>7626.27</v>
@@ -2859,7 +2859,7 @@
         <v>30</v>
       </c>
       <c r="F87" t="n">
-        <v>2394</v>
+        <v>2361</v>
       </c>
       <c r="G87" t="n">
         <v>1694.07</v>
@@ -2887,7 +2887,7 @@
         <v>22</v>
       </c>
       <c r="F88" t="n">
-        <v>1888</v>
+        <v>1877</v>
       </c>
       <c r="G88" t="n">
         <v>5082.21</v>
@@ -2915,7 +2915,7 @@
         <v>66</v>
       </c>
       <c r="F89" t="n">
-        <v>15418</v>
+        <v>15044</v>
       </c>
       <c r="G89" t="n">
         <v>1694.07</v>
@@ -2943,7 +2943,7 @@
         <v>23</v>
       </c>
       <c r="F90" t="n">
-        <v>2349</v>
+        <v>2304</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2971,13 +2971,13 @@
         <v>36</v>
       </c>
       <c r="F91" t="n">
-        <v>6952</v>
+        <v>6898</v>
       </c>
       <c r="G91" t="n">
-        <v>2032.2</v>
+        <v>1016.1</v>
       </c>
       <c r="H91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2999,7 +2999,7 @@
         <v>16</v>
       </c>
       <c r="F92" t="n">
-        <v>5354</v>
+        <v>5293</v>
       </c>
       <c r="G92" t="n">
         <v>1016.1</v>
@@ -3027,7 +3027,7 @@
         <v>8</v>
       </c>
       <c r="F93" t="n">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>101</v>
       </c>
       <c r="F95" t="n">
-        <v>9709</v>
+        <v>9564</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3111,13 +3111,13 @@
         <v>115</v>
       </c>
       <c r="F96" t="n">
-        <v>2290</v>
+        <v>2274</v>
       </c>
       <c r="G96" t="n">
-        <v>7133.04</v>
+        <v>9505.07</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
@@ -3167,7 +3167,7 @@
         <v>29</v>
       </c>
       <c r="F98" t="n">
-        <v>4013</v>
+        <v>3998</v>
       </c>
       <c r="G98" t="n">
         <v>3388.98</v>
@@ -3195,7 +3195,7 @@
         <v>147</v>
       </c>
       <c r="F99" t="n">
-        <v>10134</v>
+        <v>9926</v>
       </c>
       <c r="G99" t="n">
         <v>5931.36</v>
@@ -3223,7 +3223,7 @@
         <v>94</v>
       </c>
       <c r="F100" t="n">
-        <v>4895</v>
+        <v>4859</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>31</v>
       </c>
       <c r="F101" t="n">
-        <v>1769</v>
+        <v>1746</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3307,7 +3307,7 @@
         <v>17</v>
       </c>
       <c r="F103" t="n">
-        <v>3568</v>
+        <v>3533</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>39</v>
       </c>
       <c r="F105" t="n">
-        <v>5143</v>
+        <v>5029</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>2966</v>
+        <v>2931</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3475,7 +3475,7 @@
         <v>26</v>
       </c>
       <c r="F109" t="n">
-        <v>4867</v>
+        <v>4863</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>17</v>
       </c>
       <c r="F110" t="n">
-        <v>3024</v>
+        <v>3016</v>
       </c>
       <c r="G110" t="n">
         <v>1185.59</v>
@@ -3531,7 +3531,7 @@
         <v>68</v>
       </c>
       <c r="F111" t="n">
-        <v>4934</v>
+        <v>4896</v>
       </c>
       <c r="G111" t="n">
         <v>4744.06</v>
@@ -3587,7 +3587,7 @@
         <v>14</v>
       </c>
       <c r="F113" t="n">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>6</v>
       </c>
       <c r="F114" t="n">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>9</v>
       </c>
       <c r="F115" t="n">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3671,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         <v>11</v>
       </c>
       <c r="F118" t="n">
-        <v>1680</v>
+        <v>1666</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>16</v>
       </c>
       <c r="F121" t="n">
-        <v>2167</v>
+        <v>2158</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3839,7 +3839,7 @@
         <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         <v>9</v>
       </c>
       <c r="F124" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G124" t="n">
         <v>1948.31</v>
@@ -3923,7 +3923,7 @@
         <v>15</v>
       </c>
       <c r="F125" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>8</v>
       </c>
       <c r="F126" t="n">
-        <v>1235</v>
+        <v>1214</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4203,7 +4203,7 @@
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>4</v>
       </c>
       <c r="F136" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         <v>26</v>
       </c>
       <c r="F140" t="n">
-        <v>15962</v>
+        <v>15865</v>
       </c>
       <c r="G140" t="n">
         <v>2244.92</v>
@@ -4371,7 +4371,7 @@
         <v>8</v>
       </c>
       <c r="F141" t="n">
-        <v>2024</v>
+        <v>2001</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>3034</v>
+        <v>2984</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4483,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="F145" t="n">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         <v>4</v>
       </c>
       <c r="F147" t="n">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>2014</v>
+        <v>1994</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>14</v>
       </c>
       <c r="F151" t="n">
-        <v>4023</v>
+        <v>3996</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
         <v>194</v>
       </c>
       <c r="F153" t="n">
-        <v>17072</v>
+        <v>16864</v>
       </c>
       <c r="G153" t="n">
         <v>4235.6</v>
@@ -4735,7 +4735,7 @@
         <v>12</v>
       </c>
       <c r="F154" t="n">
-        <v>10843</v>
+        <v>10795</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4791,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>3103</v>
+        <v>3087</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>10</v>
       </c>
       <c r="F158" t="n">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G158" t="n">
         <v>1143.22</v>
@@ -4875,7 +4875,7 @@
         <v>8</v>
       </c>
       <c r="F159" t="n">
-        <v>2204</v>
+        <v>2194</v>
       </c>
       <c r="G159" t="n">
         <v>1355.08</v>
@@ -4903,7 +4903,7 @@
         <v>178</v>
       </c>
       <c r="F160" t="n">
-        <v>32185</v>
+        <v>31947</v>
       </c>
       <c r="G160" t="n">
         <v>7201.69</v>
@@ -4931,7 +4931,7 @@
         <v>5</v>
       </c>
       <c r="F161" t="n">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4959,7 +4959,7 @@
         <v>2</v>
       </c>
       <c r="F162" t="n">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         <v>4</v>
       </c>
       <c r="F163" t="n">
-        <v>805</v>
+        <v>783</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
         <v>3</v>
       </c>
       <c r="F164" t="n">
-        <v>6210</v>
+        <v>6104</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="F166" t="n">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>33</v>
       </c>
       <c r="F167" t="n">
-        <v>7370</v>
+        <v>7282</v>
       </c>
       <c r="G167" t="n">
         <v>3219.49</v>
@@ -5127,7 +5127,7 @@
         <v>6</v>
       </c>
       <c r="F168" t="n">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>4</v>
       </c>
       <c r="F170" t="n">
-        <v>1278</v>
+        <v>1250</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5239,7 +5239,7 @@
         <v>4</v>
       </c>
       <c r="F172" t="n">
-        <v>2879</v>
+        <v>2869</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
         <v>13</v>
       </c>
       <c r="F173" t="n">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
         <v>30</v>
       </c>
       <c r="F174" t="n">
-        <v>8647</v>
+        <v>8588</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>42</v>
       </c>
       <c r="F176" t="n">
-        <v>9282</v>
+        <v>8924</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>19</v>
       </c>
       <c r="F177" t="n">
-        <v>4447</v>
+        <v>4323</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>1224</v>
+        <v>1211</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5491,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5519,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>1329</v>
+        <v>1320</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
         <v>6</v>
       </c>
       <c r="F185" t="n">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="F186" t="n">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5687,7 +5687,7 @@
         <v>16</v>
       </c>
       <c r="F188" t="n">
-        <v>2558</v>
+        <v>2548</v>
       </c>
       <c r="G188" t="n">
         <v>4744.06</v>
@@ -5715,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5827,7 +5827,7 @@
         <v>2</v>
       </c>
       <c r="F193" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5883,7 +5883,7 @@
         <v>16</v>
       </c>
       <c r="F195" t="n">
-        <v>4096</v>
+        <v>4045</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>38</v>
       </c>
       <c r="F199" t="n">
-        <v>12271</v>
+        <v>12190</v>
       </c>
       <c r="G199" t="n">
         <v>1694.07</v>
@@ -6023,7 +6023,7 @@
         <v>2</v>
       </c>
       <c r="F200" t="n">
-        <v>726</v>
+        <v>693</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -6079,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>11</v>
       </c>
       <c r="F203" t="n">
-        <v>1440</v>
+        <v>1396</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>7</v>
       </c>
       <c r="F204" t="n">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6163,7 +6163,7 @@
         <v>3</v>
       </c>
       <c r="F205" t="n">
-        <v>1122</v>
+        <v>1095</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6219,7 +6219,7 @@
         <v>4</v>
       </c>
       <c r="F207" t="n">
-        <v>977</v>
+        <v>968</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
         <v>53</v>
       </c>
       <c r="F209" t="n">
-        <v>7606</v>
+        <v>7521</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6359,7 +6359,7 @@
         <v>4</v>
       </c>
       <c r="F212" t="n">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
         <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>2</v>
       </c>
       <c r="F215" t="n">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>9</v>
       </c>
       <c r="F216" t="n">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6499,7 +6499,7 @@
         <v>8</v>
       </c>
       <c r="F217" t="n">
-        <v>2128</v>
+        <v>2112</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>7</v>
       </c>
       <c r="F218" t="n">
-        <v>4196</v>
+        <v>4178</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
         <v>43</v>
       </c>
       <c r="F220" t="n">
-        <v>4340</v>
+        <v>4219</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>17</v>
       </c>
       <c r="F221" t="n">
-        <v>1988</v>
+        <v>1961</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
         <v>14</v>
       </c>
       <c r="F222" t="n">
-        <v>2396</v>
+        <v>2338</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6667,7 +6667,7 @@
         <v>3</v>
       </c>
       <c r="F223" t="n">
-        <v>854</v>
+        <v>836</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6695,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6723,7 +6723,7 @@
         <v>11</v>
       </c>
       <c r="F225" t="n">
-        <v>1957</v>
+        <v>1931</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6863,7 +6863,7 @@
         <v>311</v>
       </c>
       <c r="F230" t="n">
-        <v>38223</v>
+        <v>37807</v>
       </c>
       <c r="G230" t="n">
         <v>7879.66</v>
@@ -6919,7 +6919,7 @@
         <v>71</v>
       </c>
       <c r="F232" t="n">
-        <v>6522</v>
+        <v>6367</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>121</v>
       </c>
       <c r="F233" t="n">
-        <v>16221</v>
+        <v>15964</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
         <v>39</v>
       </c>
       <c r="F236" t="n">
-        <v>5137</v>
+        <v>5055</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7059,7 +7059,7 @@
         <v>13</v>
       </c>
       <c r="F237" t="n">
-        <v>2467</v>
+        <v>2439</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7087,7 +7087,7 @@
         <v>43</v>
       </c>
       <c r="F238" t="n">
-        <v>7188</v>
+        <v>7042</v>
       </c>
       <c r="G238" t="n">
         <v>4660.17</v>
@@ -7143,7 +7143,7 @@
         <v>603</v>
       </c>
       <c r="F240" t="n">
-        <v>61674</v>
+        <v>61353</v>
       </c>
       <c r="G240" t="n">
         <v>5931.36</v>
@@ -7171,7 +7171,7 @@
         <v>57</v>
       </c>
       <c r="F241" t="n">
-        <v>8570</v>
+        <v>8549</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7283,7 +7283,7 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7314,10 +7314,10 @@
         <v>645</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>9575.42</v>
       </c>
       <c r="H246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -7339,7 +7339,7 @@
         <v>12</v>
       </c>
       <c r="F247" t="n">
-        <v>3705</v>
+        <v>3682</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
         <v>49</v>
       </c>
       <c r="F248" t="n">
-        <v>5046</v>
+        <v>5015</v>
       </c>
       <c r="G248" t="n">
         <v>5931.36</v>
@@ -7395,7 +7395,7 @@
         <v>11</v>
       </c>
       <c r="F249" t="n">
-        <v>1185</v>
+        <v>1177</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
         <v>37</v>
       </c>
       <c r="F250" t="n">
-        <v>3333</v>
+        <v>3254</v>
       </c>
       <c r="G250" t="n">
         <v>5931.36</v>
@@ -7451,13 +7451,13 @@
         <v>90</v>
       </c>
       <c r="F251" t="n">
-        <v>3668</v>
+        <v>3642</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="H251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -7479,7 +7479,7 @@
         <v>77</v>
       </c>
       <c r="F252" t="n">
-        <v>3711</v>
+        <v>3678</v>
       </c>
       <c r="G252" t="n">
         <v>5507.63</v>
@@ -7507,7 +7507,7 @@
         <v>95</v>
       </c>
       <c r="F253" t="n">
-        <v>7014</v>
+        <v>6968</v>
       </c>
       <c r="G253" t="n">
         <v>7033.05</v>
@@ -7535,7 +7535,7 @@
         <v>47</v>
       </c>
       <c r="F254" t="n">
-        <v>4966</v>
+        <v>4926</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7563,7 +7563,7 @@
         <v>4</v>
       </c>
       <c r="F255" t="n">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7591,7 +7591,7 @@
         <v>29</v>
       </c>
       <c r="F256" t="n">
-        <v>2136</v>
+        <v>2112</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>1</v>
       </c>
       <c r="F258" t="n">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
         <v>27</v>
       </c>
       <c r="F260" t="n">
-        <v>8729</v>
+        <v>8710</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -7731,7 +7731,7 @@
         <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>3221</v>
+        <v>3208</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -7759,7 +7759,7 @@
         <v>17</v>
       </c>
       <c r="F262" t="n">
-        <v>2761</v>
+        <v>2757</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7815,7 +7815,7 @@
         <v>89</v>
       </c>
       <c r="F264" t="n">
-        <v>10251</v>
+        <v>10007</v>
       </c>
       <c r="G264" t="n">
         <v>2244.92</v>
@@ -7899,7 +7899,7 @@
         <v>22</v>
       </c>
       <c r="F267" t="n">
-        <v>2136</v>
+        <v>2127</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -8039,7 +8039,7 @@
         <v>13</v>
       </c>
       <c r="F272" t="n">
-        <v>2152</v>
+        <v>2134</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
         <v>5</v>
       </c>
       <c r="F273" t="n">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -8123,7 +8123,7 @@
         <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -8151,7 +8151,7 @@
         <v>1</v>
       </c>
       <c r="F276" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -8207,7 +8207,7 @@
         <v>18</v>
       </c>
       <c r="F278" t="n">
-        <v>2394</v>
+        <v>2378</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -8235,7 +8235,7 @@
         <v>13</v>
       </c>
       <c r="F279" t="n">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="G279" t="n">
         <v>0</v>
@@ -8263,7 +8263,7 @@
         <v>9</v>
       </c>
       <c r="F280" t="n">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8291,7 +8291,7 @@
         <v>20</v>
       </c>
       <c r="F281" t="n">
-        <v>1057</v>
+        <v>1003</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -8319,7 +8319,7 @@
         <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -8347,7 +8347,7 @@
         <v>3</v>
       </c>
       <c r="F283" t="n">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>18</v>
       </c>
       <c r="F286" t="n">
-        <v>2193</v>
+        <v>2187</v>
       </c>
       <c r="G286" t="n">
         <v>550</v>
@@ -8459,7 +8459,7 @@
         <v>5</v>
       </c>
       <c r="F287" t="n">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>6</v>
       </c>
       <c r="F289" t="n">
-        <v>1105</v>
+        <v>1087</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -8543,7 +8543,7 @@
         <v>34</v>
       </c>
       <c r="F290" t="n">
-        <v>7333</v>
+        <v>7301</v>
       </c>
       <c r="G290" t="n">
         <v>1694.07</v>
@@ -8599,7 +8599,7 @@
         <v>7</v>
       </c>
       <c r="F292" t="n">
-        <v>1979</v>
+        <v>1893</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -8627,7 +8627,7 @@
         <v>3</v>
       </c>
       <c r="F293" t="n">
-        <v>1587</v>
+        <v>1545</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -8655,7 +8655,7 @@
         <v>15</v>
       </c>
       <c r="F294" t="n">
-        <v>8898</v>
+        <v>8516</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
         <v>8</v>
       </c>
       <c r="F295" t="n">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -8711,7 +8711,7 @@
         <v>23</v>
       </c>
       <c r="F296" t="n">
-        <v>2550</v>
+        <v>2501</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -8739,7 +8739,7 @@
         <v>10</v>
       </c>
       <c r="F297" t="n">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G297" t="n">
         <v>0</v>
@@ -8767,7 +8767,7 @@
         <v>15</v>
       </c>
       <c r="F298" t="n">
-        <v>2460</v>
+        <v>2433</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -8795,7 +8795,7 @@
         <v>37</v>
       </c>
       <c r="F299" t="n">
-        <v>6755</v>
+        <v>6636</v>
       </c>
       <c r="G299" t="n">
         <v>2727.11</v>
@@ -8823,7 +8823,7 @@
         <v>46</v>
       </c>
       <c r="F300" t="n">
-        <v>4021</v>
+        <v>3931</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
         <v>3</v>
       </c>
       <c r="F301" t="n">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="G301" t="n">
         <v>0</v>
@@ -8879,7 +8879,7 @@
         <v>9</v>
       </c>
       <c r="F302" t="n">
-        <v>1176</v>
+        <v>1167</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         <v>82</v>
       </c>
       <c r="F303" t="n">
-        <v>12801</v>
+        <v>12735</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -8935,7 +8935,7 @@
         <v>14</v>
       </c>
       <c r="F304" t="n">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -8963,7 +8963,7 @@
         <v>23</v>
       </c>
       <c r="F305" t="n">
-        <v>4433</v>
+        <v>4338</v>
       </c>
       <c r="G305" t="n">
         <v>0</v>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="F308" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
         <v>4</v>
       </c>
       <c r="F309" t="n">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="F310" t="n">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>9</v>
       </c>
       <c r="F315" t="n">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
         <v>2</v>
       </c>
       <c r="F317" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G317" t="n">
         <v>0</v>
@@ -9495,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="F324" t="n">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
         <v>3</v>
       </c>
       <c r="F326" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>14</v>
       </c>
       <c r="F329" t="n">
-        <v>1174</v>
+        <v>1166</v>
       </c>
       <c r="G329" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
         <v>5</v>
       </c>
       <c r="F331" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G331" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>4</v>
       </c>
       <c r="F332" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G332" t="n">
         <v>0</v>
@@ -9747,7 +9747,7 @@
         <v>35</v>
       </c>
       <c r="F333" t="n">
-        <v>3801</v>
+        <v>3782</v>
       </c>
       <c r="G333" t="n">
         <v>8133.9</v>
@@ -9775,7 +9775,7 @@
         <v>111</v>
       </c>
       <c r="F334" t="n">
-        <v>10261</v>
+        <v>10209</v>
       </c>
       <c r="G334" t="n">
         <v>5803.39</v>
@@ -9831,7 +9831,7 @@
         <v>1</v>
       </c>
       <c r="F336" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -9859,7 +9859,7 @@
         <v>1</v>
       </c>
       <c r="F337" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="G337" t="n">
         <v>0</v>
@@ -9887,7 +9887,7 @@
         <v>2</v>
       </c>
       <c r="F338" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G338" t="n">
         <v>0</v>
@@ -9943,7 +9943,7 @@
         <v>1</v>
       </c>
       <c r="F340" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G340" t="n">
         <v>0</v>
@@ -9971,7 +9971,7 @@
         <v>5</v>
       </c>
       <c r="F341" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G341" t="n">
         <v>0</v>
@@ -9999,7 +9999,7 @@
         <v>10</v>
       </c>
       <c r="F342" t="n">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G342" t="n">
         <v>0</v>
@@ -10027,7 +10027,7 @@
         <v>2</v>
       </c>
       <c r="F343" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G343" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="F344" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
@@ -10083,7 +10083,7 @@
         <v>7</v>
       </c>
       <c r="F345" t="n">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G345" t="n">
         <v>0</v>
@@ -10139,7 +10139,7 @@
         <v>5</v>
       </c>
       <c r="F347" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G347" t="n">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>7</v>
       </c>
       <c r="F348" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G348" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>36</v>
       </c>
       <c r="F349" t="n">
-        <v>3103</v>
+        <v>3089</v>
       </c>
       <c r="G349" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
         <v>4</v>
       </c>
       <c r="F350" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G350" t="n">
         <v>0</v>
@@ -10307,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="F353" t="n">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
@@ -10335,7 +10335,7 @@
         <v>8</v>
       </c>
       <c r="F354" t="n">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="G354" t="n">
         <v>0</v>
@@ -10363,7 +10363,7 @@
         <v>24</v>
       </c>
       <c r="F355" t="n">
-        <v>3183</v>
+        <v>3176</v>
       </c>
       <c r="G355" t="n">
         <v>0</v>
@@ -10478,10 +10478,10 @@
         <v>23</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>2372.03</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -10503,7 +10503,7 @@
         <v>11</v>
       </c>
       <c r="F360" t="n">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="G360" t="n">
         <v>0</v>
@@ -10727,7 +10727,7 @@
         <v>2</v>
       </c>
       <c r="F368" t="n">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G368" t="n">
         <v>0</v>
@@ -10755,7 +10755,7 @@
         <v>0</v>
       </c>
       <c r="F369" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G369" t="n">
         <v>0</v>
@@ -10783,7 +10783,7 @@
         <v>2</v>
       </c>
       <c r="F370" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G370" t="n">
         <v>0</v>
@@ -10923,13 +10923,13 @@
         <v>31</v>
       </c>
       <c r="F375" t="n">
-        <v>2695</v>
+        <v>2671</v>
       </c>
       <c r="G375" t="n">
         <v>3716.96</v>
       </c>
       <c r="H375" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="376">
@@ -10951,7 +10951,7 @@
         <v>12</v>
       </c>
       <c r="F376" t="n">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="G376" t="n">
         <v>0</v>
@@ -11063,7 +11063,7 @@
         <v>6</v>
       </c>
       <c r="F380" t="n">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="G380" t="n">
         <v>0</v>
@@ -11119,7 +11119,7 @@
         <v>3</v>
       </c>
       <c r="F382" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -11147,7 +11147,7 @@
         <v>1</v>
       </c>
       <c r="F383" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G383" t="n">
         <v>0</v>
@@ -11203,7 +11203,7 @@
         <v>11</v>
       </c>
       <c r="F385" t="n">
-        <v>1858</v>
+        <v>1854</v>
       </c>
       <c r="G385" t="n">
         <v>0</v>
@@ -11231,7 +11231,7 @@
         <v>4</v>
       </c>
       <c r="F386" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G386" t="n">
         <v>4490.68</v>
@@ -11259,7 +11259,7 @@
         <v>2</v>
       </c>
       <c r="F387" t="n">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="G387" t="n">
         <v>0</v>
@@ -11343,7 +11343,7 @@
         <v>0</v>
       </c>
       <c r="F390" t="n">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G390" t="n">
         <v>0</v>
@@ -11371,7 +11371,7 @@
         <v>4</v>
       </c>
       <c r="F391" t="n">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G391" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>13</v>
       </c>
       <c r="F394" t="n">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="G394" t="n">
         <v>1016.1</v>
@@ -11483,7 +11483,7 @@
         <v>8</v>
       </c>
       <c r="F395" t="n">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G395" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
         <v>11</v>
       </c>
       <c r="F397" t="n">
-        <v>1642</v>
+        <v>1630</v>
       </c>
       <c r="G397" t="n">
         <v>9829.66</v>
@@ -11735,7 +11735,7 @@
         <v>2</v>
       </c>
       <c r="F404" t="n">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="G404" t="n">
         <v>0</v>
@@ -11763,7 +11763,7 @@
         <v>2</v>
       </c>
       <c r="F405" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G405" t="n">
         <v>0</v>
@@ -11791,7 +11791,7 @@
         <v>0</v>
       </c>
       <c r="F406" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G406" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
         <v>21</v>
       </c>
       <c r="F411" t="n">
-        <v>1689</v>
+        <v>1675</v>
       </c>
       <c r="G411" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
         <v>18</v>
       </c>
       <c r="F412" t="n">
-        <v>1648</v>
+        <v>1634</v>
       </c>
       <c r="G412" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="F416" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G416" t="n">
         <v>0</v>
@@ -12155,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="F419" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
@@ -12183,7 +12183,7 @@
         <v>6</v>
       </c>
       <c r="F420" t="n">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G420" t="n">
         <v>0</v>
@@ -12239,7 +12239,7 @@
         <v>27</v>
       </c>
       <c r="F422" t="n">
-        <v>3539</v>
+        <v>3512</v>
       </c>
       <c r="G422" t="n">
         <v>0</v>
@@ -12267,7 +12267,7 @@
         <v>114</v>
       </c>
       <c r="F423" t="n">
-        <v>7570</v>
+        <v>7520</v>
       </c>
       <c r="G423" t="n">
         <v>0</v>
@@ -12323,7 +12323,7 @@
         <v>26</v>
       </c>
       <c r="F425" t="n">
-        <v>1777</v>
+        <v>1770</v>
       </c>
       <c r="G425" t="n">
         <v>0</v>
@@ -12379,7 +12379,7 @@
         <v>19</v>
       </c>
       <c r="F427" t="n">
-        <v>2812</v>
+        <v>2799</v>
       </c>
       <c r="G427" t="n">
         <v>0</v>
@@ -12407,7 +12407,7 @@
         <v>24</v>
       </c>
       <c r="F428" t="n">
-        <v>4104</v>
+        <v>4083</v>
       </c>
       <c r="G428" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>11</v>
       </c>
       <c r="F431" t="n">
-        <v>1576</v>
+        <v>1564</v>
       </c>
       <c r="G431" t="n">
         <v>0</v>
@@ -12519,7 +12519,7 @@
         <v>10</v>
       </c>
       <c r="F432" t="n">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="G432" t="n">
         <v>0</v>
@@ -12547,7 +12547,7 @@
         <v>0</v>
       </c>
       <c r="F433" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G433" t="n">
         <v>0</v>
@@ -12575,7 +12575,7 @@
         <v>6</v>
       </c>
       <c r="F434" t="n">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="G434" t="n">
         <v>0</v>
@@ -12603,7 +12603,7 @@
         <v>5</v>
       </c>
       <c r="F435" t="n">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G435" t="n">
         <v>3388.98</v>
@@ -12687,7 +12687,7 @@
         <v>4</v>
       </c>
       <c r="F438" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G438" t="n">
         <v>0</v>
@@ -12743,7 +12743,7 @@
         <v>3</v>
       </c>
       <c r="F440" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G440" t="n">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>4</v>
       </c>
       <c r="F441" t="n">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G441" t="n">
         <v>0</v>
@@ -12939,7 +12939,7 @@
         <v>12</v>
       </c>
       <c r="F447" t="n">
-        <v>4854</v>
+        <v>4826</v>
       </c>
       <c r="G447" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
         <v>2</v>
       </c>
       <c r="F448" t="n">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G448" t="n">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         <v>1</v>
       </c>
       <c r="F450" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G450" t="n">
         <v>0</v>
@@ -13051,7 +13051,7 @@
         <v>1</v>
       </c>
       <c r="F451" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G451" t="n">
         <v>0</v>
@@ -13079,7 +13079,7 @@
         <v>41</v>
       </c>
       <c r="F452" t="n">
-        <v>4086</v>
+        <v>4068</v>
       </c>
       <c r="G452" t="n">
         <v>0</v>
@@ -13135,7 +13135,7 @@
         <v>17</v>
       </c>
       <c r="F454" t="n">
-        <v>3288</v>
+        <v>3255</v>
       </c>
       <c r="G454" t="n">
         <v>550</v>
@@ -13163,7 +13163,7 @@
         <v>32</v>
       </c>
       <c r="F455" t="n">
-        <v>4373</v>
+        <v>4293</v>
       </c>
       <c r="G455" t="n">
         <v>0</v>
@@ -13247,7 +13247,7 @@
         <v>20</v>
       </c>
       <c r="F458" t="n">
-        <v>5334</v>
+        <v>5264</v>
       </c>
       <c r="G458" t="n">
         <v>1491.98</v>
@@ -13275,7 +13275,7 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>1484</v>
+        <v>1399</v>
       </c>
       <c r="G459" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>5</v>
       </c>
       <c r="F460" t="n">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="G460" t="n">
         <v>0</v>
@@ -13359,7 +13359,7 @@
         <v>17</v>
       </c>
       <c r="F462" t="n">
-        <v>4431</v>
+        <v>4346</v>
       </c>
       <c r="G462" t="n">
         <v>1802.54</v>
@@ -13387,7 +13387,7 @@
         <v>0</v>
       </c>
       <c r="F463" t="n">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="G463" t="n">
         <v>0</v>
@@ -13415,7 +13415,7 @@
         <v>4</v>
       </c>
       <c r="F464" t="n">
-        <v>1028</v>
+        <v>1001</v>
       </c>
       <c r="G464" t="n">
         <v>0</v>
@@ -13443,7 +13443,7 @@
         <v>10</v>
       </c>
       <c r="F465" t="n">
-        <v>2225</v>
+        <v>2206</v>
       </c>
       <c r="G465" t="n">
         <v>0</v>
@@ -13471,7 +13471,7 @@
         <v>1</v>
       </c>
       <c r="F466" t="n">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="G466" t="n">
         <v>0</v>
@@ -13499,7 +13499,7 @@
         <v>0</v>
       </c>
       <c r="F467" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="G467" t="n">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>0</v>
       </c>
       <c r="F468" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G468" t="n">
         <v>0</v>
@@ -13555,7 +13555,7 @@
         <v>4</v>
       </c>
       <c r="F469" t="n">
-        <v>1872</v>
+        <v>1861</v>
       </c>
       <c r="G469" t="n">
         <v>0</v>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="F470" t="n">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="G470" t="n">
         <v>0</v>
@@ -13611,7 +13611,7 @@
         <v>9</v>
       </c>
       <c r="F471" t="n">
-        <v>2306</v>
+        <v>2262</v>
       </c>
       <c r="G471" t="n">
         <v>0</v>
@@ -13639,7 +13639,7 @@
         <v>4</v>
       </c>
       <c r="F472" t="n">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="G472" t="n">
         <v>1694.07</v>
@@ -13667,7 +13667,7 @@
         <v>7</v>
       </c>
       <c r="F473" t="n">
-        <v>1228</v>
+        <v>1196</v>
       </c>
       <c r="G473" t="n">
         <v>0</v>
@@ -13695,7 +13695,7 @@
         <v>8</v>
       </c>
       <c r="F474" t="n">
-        <v>788</v>
+        <v>757</v>
       </c>
       <c r="G474" t="n">
         <v>2456.78</v>
@@ -13723,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="F475" t="n">
-        <v>1294</v>
+        <v>1284</v>
       </c>
       <c r="G475" t="n">
         <v>0</v>
@@ -13751,7 +13751,7 @@
         <v>10</v>
       </c>
       <c r="F476" t="n">
-        <v>1575</v>
+        <v>1555</v>
       </c>
       <c r="G476" t="n">
         <v>0</v>
@@ -13779,7 +13779,7 @@
         <v>2</v>
       </c>
       <c r="F477" t="n">
-        <v>1158</v>
+        <v>1149</v>
       </c>
       <c r="G477" t="n">
         <v>0</v>
@@ -13807,13 +13807,13 @@
         <v>19</v>
       </c>
       <c r="F478" t="n">
-        <v>5451</v>
+        <v>5400</v>
       </c>
       <c r="G478" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -13835,7 +13835,7 @@
         <v>9</v>
       </c>
       <c r="F479" t="n">
-        <v>2039</v>
+        <v>2019</v>
       </c>
       <c r="G479" t="n">
         <v>0</v>
@@ -13863,7 +13863,7 @@
         <v>6</v>
       </c>
       <c r="F480" t="n">
-        <v>1550</v>
+        <v>1542</v>
       </c>
       <c r="G480" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13932,22 +13932,22 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-Audio Interface-SD-Audience</t>
+          <t>AA_Condenser_AM-C1_SD_PT (Self)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>601.12</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8934</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -13960,50 +13960,50 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Audio Array-B0FG88HVQ8-DJ Headphone-SD-PT</t>
+          <t>AA_Condenser_AM-C1_SD_PT (Self)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>359.87</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7546</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3388.14</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-SD-CT</t>
+          <t>AA_Studio_Monitor_AM-S1_SD_In-Marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>160.62</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>19125</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -14016,56 +14016,56 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-SD-CT</t>
+          <t>Audio Array-B0BPLZ5CGV-Audio Interface-SD-Audience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>88.95999999999999</v>
+        <v>601.12</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>13142</v>
+        <v>8934</v>
       </c>
       <c r="G5" t="n">
-        <v>1439.84</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-SD-CT</t>
+          <t>Audio Array-B0FG88HVQ8-DJ Headphone-SD-PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>793.96</v>
+        <v>359.87</v>
       </c>
       <c r="E6" t="n">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>30874</v>
+        <v>7546</v>
       </c>
       <c r="G6" t="n">
-        <v>4066.95</v>
+        <v>3388.14</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -14077,23 +14077,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>132.44</v>
+        <v>160.62</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>8926</v>
+        <v>19073</v>
       </c>
       <c r="G7" t="n">
-        <v>8598.32</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -14105,23 +14105,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>129.1</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n">
-        <v>8723</v>
+        <v>13135</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1439.84</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -14161,17 +14161,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>376.16</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>88327</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -14189,17 +14189,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>495.01</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>17167</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -14217,17 +14217,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>117.31</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>5871</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -14245,23 +14245,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>31.96</v>
+        <v>793.96</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="F13" t="n">
-        <v>1066</v>
+        <v>30874</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4066.95</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14273,51 +14273,891 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>883.48</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>662</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>160942</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5931.36</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0CH4RNWJX</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>132.44</v>
+      </c>
+      <c r="E15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8906</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10843.24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0CKHVHVQ1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0CM6NTWBP</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8723</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0CM6NVLT9</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0CM6WH4ZT</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0CM9KJZWQ</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0CM9L1QZG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0CM9P5CCK</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0D3LZWTHV</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0D3M1B4Z8</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DN6MNS1X</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DN6PFWNK</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0DXFPM4N2</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="E27" t="n">
+        <v>250</v>
+      </c>
+      <c r="F27" t="n">
+        <v>88322</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0FPR7VFCH</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0FPR962YS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0FVM17Q4W</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0G53H49BS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>495.01</v>
+      </c>
+      <c r="E34" t="n">
+        <v>98</v>
+      </c>
+      <c r="F34" t="n">
+        <v>17115</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0G53M9258</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0GCP1J2HC</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>117.31</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5865</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0GKPXQ8G3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0GN2LHJY4</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0GN97RFPR</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>883.48</v>
+      </c>
+      <c r="E39" t="n">
+        <v>662</v>
+      </c>
+      <c r="F39" t="n">
+        <v>160938</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5931.36</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0GW8R2RYM</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0GW8VBCBL</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0GW8Z556N</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array-Catch All-SD-CT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Audio Array-Multi Ad group-Condenser-SD-PT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>B0B4DPX2J2</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D44" t="n">
         <v>722.53</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E44" t="n">
         <v>62</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F44" t="n">
         <v>14815</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G44" t="n">
         <v>2244.92</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H44" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AudioArray-B0FFB6YJM1-Soundbar_SD_Video-PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0FFB6YJM1</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14394,7 +15234,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4142</v>
+        <v>4115</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
@@ -14427,7 +15267,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2760</v>
+        <v>2742</v>
       </c>
       <c r="E3" t="n">
         <v>36</v>
@@ -14460,7 +15300,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10694</v>
+        <v>10645</v>
       </c>
       <c r="E4" t="n">
         <v>86</v>
@@ -14493,7 +15333,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
@@ -14526,7 +15366,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1877</v>
+        <v>1869</v>
       </c>
       <c r="E6" t="n">
         <v>35</v>
@@ -14559,7 +15399,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3398</v>
+        <v>3380</v>
       </c>
       <c r="E7" t="n">
         <v>28</v>
@@ -14592,7 +15432,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3398</v>
+        <v>3380</v>
       </c>
       <c r="E8" t="n">
         <v>28</v>
@@ -14625,7 +15465,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3398</v>
+        <v>3380</v>
       </c>
       <c r="E9" t="n">
         <v>28</v>
@@ -14658,7 +15498,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -14691,7 +15531,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
@@ -14724,7 +15564,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E12" t="n">
         <v>4</v>
@@ -14757,7 +15597,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -14790,7 +15630,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -14823,7 +15663,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -14856,7 +15696,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4942</v>
+        <v>4918</v>
       </c>
       <c r="E16" t="n">
         <v>29</v>
@@ -14889,7 +15729,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -14922,7 +15762,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -14955,7 +15795,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -14988,7 +15828,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
@@ -15021,7 +15861,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -15054,7 +15894,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -15087,7 +15927,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
@@ -15120,7 +15960,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -15153,7 +15993,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -15186,7 +16026,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -15219,7 +16059,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E27" t="n">
         <v>4</v>
@@ -15252,7 +16092,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
@@ -15285,7 +16125,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
@@ -15318,7 +16158,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
@@ -15351,7 +16191,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
@@ -15384,7 +16224,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E32" t="n">
         <v>4</v>
@@ -15417,7 +16257,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E33" t="n">
         <v>4</v>
@@ -15450,7 +16290,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E34" t="n">
         <v>4</v>
@@ -15483,7 +16323,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
@@ -15516,7 +16356,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E36" t="n">
         <v>4</v>
@@ -15549,7 +16389,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E37" t="n">
         <v>4</v>
@@ -15582,7 +16422,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="E38" t="n">
         <v>4</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
@@ -14731,7 +14731,7 @@
         <v>698</v>
       </c>
       <c r="F8" t="n">
-        <v>195963</v>
+        <v>195962</v>
       </c>
       <c r="G8" t="n">
         <v>5802.55</v>
@@ -15291,7 +15291,7 @@
         <v>1991</v>
       </c>
       <c r="F28" t="n">
-        <v>565026</v>
+        <v>565025</v>
       </c>
       <c r="G28" t="n">
         <v>21183.9</v>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3687.71</v>
+        <v>3686.17</v>
       </c>
       <c r="E35" t="n">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F35" t="n">
         <v>152549</v>
@@ -15627,7 +15627,7 @@
         <v>4059</v>
       </c>
       <c r="F40" t="n">
-        <v>1004726</v>
+        <v>1004724</v>
       </c>
       <c r="G40" t="n">
         <v>20250.85</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
@@ -4623,7 +4623,7 @@
         <v>124</v>
       </c>
       <c r="F150" t="n">
-        <v>75719</v>
+        <v>75718</v>
       </c>
       <c r="G150" t="n">
         <v>6877.98</v>
@@ -7451,7 +7451,7 @@
         <v>3900</v>
       </c>
       <c r="F251" t="n">
-        <v>399755</v>
+        <v>399752</v>
       </c>
       <c r="G251" t="n">
         <v>21861.03</v>
@@ -8683,7 +8683,7 @@
         <v>90</v>
       </c>
       <c r="F295" t="n">
-        <v>17551</v>
+        <v>17550</v>
       </c>
       <c r="G295" t="n">
         <v>5123.74</v>
@@ -9299,7 +9299,7 @@
         <v>43</v>
       </c>
       <c r="F317" t="n">
-        <v>9737</v>
+        <v>9735</v>
       </c>
       <c r="G317" t="n">
         <v>6523.72</v>
@@ -13978,10 +13978,10 @@
         <v>36715</v>
       </c>
       <c r="G484" t="n">
-        <v>7054.24</v>
+        <v>8748.309999999999</v>
       </c>
       <c r="H484" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="485">
@@ -15627,7 +15627,7 @@
         <v>4059</v>
       </c>
       <c r="F40" t="n">
-        <v>1004724</v>
+        <v>1004717</v>
       </c>
       <c r="G40" t="n">
         <v>20250.85</v>
@@ -16274,19 +16274,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19689</v>
+        <v>16006</v>
       </c>
       <c r="E14" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>877.8286585040379</v>
+        <v>713.6148785311477</v>
       </c>
       <c r="G14" t="n">
-        <v>8337.673040731492</v>
+        <v>6777.96</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -16307,16 +16307,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23131</v>
+        <v>18804</v>
       </c>
       <c r="E15" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="F15" t="n">
-        <v>1031.26955833957</v>
+        <v>838.3518736577879</v>
       </c>
       <c r="G15" t="n">
-        <v>9795.064573248215</v>
+        <v>7962.719999999999</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -16439,19 +16439,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12799</v>
+        <v>20809</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="F19" t="n">
-        <v>570.6217831563916</v>
+        <v>927.7532478110641</v>
       </c>
       <c r="G19" t="n">
-        <v>5419.802386020294</v>
+        <v>8811.860000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
@@ -731,7 +731,7 @@
         <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>13395</v>
+        <v>13394</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
         <v>27</v>
       </c>
       <c r="F24" t="n">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>26811.92</v>
       </c>
       <c r="H25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1266,10 +1266,10 @@
         <v>25140</v>
       </c>
       <c r="G30" t="n">
-        <v>60978.91</v>
+        <v>63223.83</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -1431,7 +1431,7 @@
         <v>51</v>
       </c>
       <c r="F36" t="n">
-        <v>8519</v>
+        <v>8517</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1490,10 +1490,10 @@
         <v>7323</v>
       </c>
       <c r="G38" t="n">
-        <v>6250</v>
+        <v>7689.83</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -1767,7 +1767,7 @@
         <v>254</v>
       </c>
       <c r="F48" t="n">
-        <v>46608</v>
+        <v>46606</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>12200.84</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2859.41</v>
+        <v>2856.57</v>
       </c>
       <c r="E51" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F51" t="n">
-        <v>47487</v>
+        <v>47485</v>
       </c>
       <c r="G51" t="n">
         <v>28555.92</v>
@@ -1938,10 +1938,10 @@
         <v>81814</v>
       </c>
       <c r="G54" t="n">
-        <v>55200</v>
+        <v>59266.95</v>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -2162,10 +2162,10 @@
         <v>30851</v>
       </c>
       <c r="G62" t="n">
-        <v>32142.36</v>
+        <v>38411.86</v>
       </c>
       <c r="H62" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
@@ -2190,10 +2190,10 @@
         <v>5788</v>
       </c>
       <c r="G63" t="n">
-        <v>12793.22</v>
+        <v>16012.71</v>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -2218,10 +2218,10 @@
         <v>38518</v>
       </c>
       <c r="G64" t="n">
-        <v>16603.42</v>
+        <v>19483.93</v>
       </c>
       <c r="H64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -2271,7 +2271,7 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>4825</v>
+        <v>4823</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2327,13 +2327,13 @@
         <v>137</v>
       </c>
       <c r="F68" t="n">
-        <v>15727</v>
+        <v>15726</v>
       </c>
       <c r="G68" t="n">
-        <v>6396.62</v>
+        <v>10802.55</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -2498,10 +2498,10 @@
         <v>5208</v>
       </c>
       <c r="G74" t="n">
-        <v>4405.93</v>
+        <v>8811.860000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2579,7 +2579,7 @@
         <v>464</v>
       </c>
       <c r="F77" t="n">
-        <v>66369</v>
+        <v>66367</v>
       </c>
       <c r="G77" t="n">
         <v>7878.81</v>
@@ -2837,7 +2837,7 @@
         <v>5676.27</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -3055,7 +3055,7 @@
         <v>435</v>
       </c>
       <c r="F94" t="n">
-        <v>91084</v>
+        <v>91083</v>
       </c>
       <c r="G94" t="n">
         <v>24564.47</v>
@@ -3142,10 +3142,10 @@
         <v>47099</v>
       </c>
       <c r="G97" t="n">
-        <v>13209.3</v>
+        <v>14225.4</v>
       </c>
       <c r="H97" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98">
@@ -3223,7 +3223,7 @@
         <v>866</v>
       </c>
       <c r="F100" t="n">
-        <v>79301</v>
+        <v>79298</v>
       </c>
       <c r="G100" t="n">
         <v>15886.44</v>
@@ -3254,10 +3254,10 @@
         <v>13685</v>
       </c>
       <c r="G101" t="n">
-        <v>46923.69</v>
+        <v>44594.03</v>
       </c>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102">
@@ -3441,13 +3441,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1279.2</v>
+        <v>1278.03</v>
       </c>
       <c r="E108" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F108" t="n">
-        <v>27997</v>
+        <v>27995</v>
       </c>
       <c r="G108" t="n">
         <v>4236.44</v>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1413.46</v>
+        <v>1409.81</v>
       </c>
       <c r="E110" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F110" t="n">
-        <v>36755</v>
+        <v>36753</v>
       </c>
       <c r="G110" t="n">
         <v>4660.17</v>
@@ -3951,7 +3951,7 @@
         <v>16</v>
       </c>
       <c r="F126" t="n">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>124</v>
       </c>
       <c r="F150" t="n">
-        <v>75718</v>
+        <v>75715</v>
       </c>
       <c r="G150" t="n">
         <v>6877.98</v>
@@ -4651,7 +4651,7 @@
         <v>37</v>
       </c>
       <c r="F151" t="n">
-        <v>8481</v>
+        <v>8480</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>14</v>
       </c>
       <c r="F152" t="n">
-        <v>10254</v>
+        <v>10251</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4735,7 +4735,7 @@
         <v>21</v>
       </c>
       <c r="F154" t="n">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4819,7 +4819,7 @@
         <v>40</v>
       </c>
       <c r="F157" t="n">
-        <v>8115</v>
+        <v>8114</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>6</v>
       </c>
       <c r="F160" t="n">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G160" t="n">
         <v>1694.07</v>
@@ -4987,7 +4987,7 @@
         <v>1503</v>
       </c>
       <c r="F163" t="n">
-        <v>127172</v>
+        <v>127170</v>
       </c>
       <c r="G163" t="n">
         <v>24400.87</v>
@@ -5015,7 +5015,7 @@
         <v>39</v>
       </c>
       <c r="F164" t="n">
-        <v>44482</v>
+        <v>44480</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
         <v>17</v>
       </c>
       <c r="F166" t="n">
-        <v>17740</v>
+        <v>17739</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>44</v>
       </c>
       <c r="F168" t="n">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="G168" t="n">
         <v>1143.22</v>
@@ -5183,7 +5183,7 @@
         <v>1163</v>
       </c>
       <c r="F170" t="n">
-        <v>206458</v>
+        <v>206452</v>
       </c>
       <c r="G170" t="n">
         <v>35247.46</v>
@@ -5267,7 +5267,7 @@
         <v>28</v>
       </c>
       <c r="F173" t="n">
-        <v>4612</v>
+        <v>4611</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5323,7 +5323,7 @@
         <v>12</v>
       </c>
       <c r="F175" t="n">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
         <v>203</v>
       </c>
       <c r="F177" t="n">
-        <v>46982</v>
+        <v>46981</v>
       </c>
       <c r="G177" t="n">
         <v>12942.37</v>
@@ -5407,7 +5407,7 @@
         <v>30</v>
       </c>
       <c r="F178" t="n">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>16</v>
       </c>
       <c r="F180" t="n">
-        <v>7492</v>
+        <v>7489</v>
       </c>
       <c r="G180" t="n">
         <v>2117.8</v>
@@ -5491,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="F181" t="n">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>289</v>
       </c>
       <c r="F186" t="n">
-        <v>60254</v>
+        <v>60249</v>
       </c>
       <c r="G186" t="n">
         <v>1312.71</v>
@@ -5653,13 +5653,13 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>502.18</v>
+        <v>501.18</v>
       </c>
       <c r="E187" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F187" t="n">
-        <v>30607</v>
+        <v>30605</v>
       </c>
       <c r="G187" t="n">
         <v>2498.3</v>
@@ -5883,7 +5883,7 @@
         <v>31</v>
       </c>
       <c r="F195" t="n">
-        <v>6034</v>
+        <v>6033</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>185.46</v>
+        <v>182.06</v>
       </c>
       <c r="E198" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F198" t="n">
-        <v>10136</v>
+        <v>10134</v>
       </c>
       <c r="G198" t="n">
         <v>4744.06</v>
@@ -6163,7 +6163,7 @@
         <v>109</v>
       </c>
       <c r="F205" t="n">
-        <v>27396</v>
+        <v>27395</v>
       </c>
       <c r="G205" t="n">
         <v>2509.34</v>
@@ -6247,13 +6247,13 @@
         <v>344</v>
       </c>
       <c r="F208" t="n">
-        <v>71041</v>
+        <v>71040</v>
       </c>
       <c r="G208" t="n">
-        <v>2032.2</v>
+        <v>3048.3</v>
       </c>
       <c r="H208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -6275,13 +6275,13 @@
         <v>193</v>
       </c>
       <c r="F209" t="n">
-        <v>62755</v>
+        <v>62754</v>
       </c>
       <c r="G209" t="n">
         <v>3388.14</v>
       </c>
       <c r="H209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -6415,7 +6415,7 @@
         <v>64</v>
       </c>
       <c r="F214" t="n">
-        <v>13849</v>
+        <v>13847</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6471,7 +6471,7 @@
         <v>23</v>
       </c>
       <c r="F216" t="n">
-        <v>6506</v>
+        <v>6505</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>40</v>
       </c>
       <c r="F218" t="n">
-        <v>9050</v>
+        <v>9049</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         <v>295</v>
       </c>
       <c r="F231" t="n">
-        <v>29529</v>
+        <v>29524</v>
       </c>
       <c r="G231" t="n">
         <v>21014.41</v>
@@ -6919,7 +6919,7 @@
         <v>197</v>
       </c>
       <c r="F232" t="n">
-        <v>17276</v>
+        <v>17275</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         <v>71</v>
       </c>
       <c r="F233" t="n">
-        <v>14855</v>
+        <v>14853</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
         <v>2330</v>
       </c>
       <c r="F241" t="n">
-        <v>303391</v>
+        <v>303385</v>
       </c>
       <c r="G241" t="n">
         <v>17240.67</v>
@@ -7227,7 +7227,7 @@
         <v>471</v>
       </c>
       <c r="F243" t="n">
-        <v>39871</v>
+        <v>39870</v>
       </c>
       <c r="G243" t="n">
         <v>11015.26</v>
@@ -7249,19 +7249,19 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2233.25</v>
+        <v>2232.25</v>
       </c>
       <c r="E244" t="n">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F244" t="n">
-        <v>122371</v>
+        <v>122368</v>
       </c>
       <c r="G244" t="n">
-        <v>13034.74</v>
+        <v>16423.72</v>
       </c>
       <c r="H244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>732.98</v>
+        <v>731.98</v>
       </c>
       <c r="E247" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F247" t="n">
-        <v>32080</v>
+        <v>32078</v>
       </c>
       <c r="G247" t="n">
         <v>4236.44</v>
@@ -7367,7 +7367,7 @@
         <v>77</v>
       </c>
       <c r="F248" t="n">
-        <v>12954</v>
+        <v>12953</v>
       </c>
       <c r="G248" t="n">
         <v>3388.98</v>
@@ -7395,7 +7395,7 @@
         <v>342</v>
       </c>
       <c r="F249" t="n">
-        <v>39979</v>
+        <v>39976</v>
       </c>
       <c r="G249" t="n">
         <v>4660.17</v>
@@ -7445,19 +7445,19 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>10353.93</v>
+        <v>10352.93</v>
       </c>
       <c r="E251" t="n">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="F251" t="n">
-        <v>399752</v>
+        <v>399747</v>
       </c>
       <c r="G251" t="n">
-        <v>21861.03</v>
+        <v>22411.03</v>
       </c>
       <c r="H251" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252">
@@ -7678,10 +7678,10 @@
         <v>32226</v>
       </c>
       <c r="G259" t="n">
-        <v>23725.44</v>
+        <v>30080.52</v>
       </c>
       <c r="H259" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260">
@@ -7762,10 +7762,10 @@
         <v>23235</v>
       </c>
       <c r="G262" t="n">
-        <v>17662.7</v>
+        <v>19992.36</v>
       </c>
       <c r="H262" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="263">
@@ -7983,7 +7983,7 @@
         <v>32</v>
       </c>
       <c r="F270" t="n">
-        <v>4882</v>
+        <v>4881</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -8039,13 +8039,13 @@
         <v>114</v>
       </c>
       <c r="F272" t="n">
-        <v>33716</v>
+        <v>33714</v>
       </c>
       <c r="G272" t="n">
-        <v>3388.98</v>
+        <v>6777.96</v>
       </c>
       <c r="H272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1306.34</v>
+        <v>1291.28</v>
       </c>
       <c r="E274" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F274" t="n">
-        <v>16461</v>
+        <v>16459</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -8210,10 +8210,10 @@
         <v>48389</v>
       </c>
       <c r="G278" t="n">
-        <v>46381.44</v>
+        <v>48626.36</v>
       </c>
       <c r="H278" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="279">
@@ -8465,7 +8465,7 @@
         <v>6776.28</v>
       </c>
       <c r="H287" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
@@ -8633,7 +8633,7 @@
         <v>4516.67</v>
       </c>
       <c r="H293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -8689,7 +8689,7 @@
         <v>5123.74</v>
       </c>
       <c r="H295" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296">
@@ -9103,7 +9103,7 @@
         <v>95</v>
       </c>
       <c r="F310" t="n">
-        <v>36591</v>
+        <v>36589</v>
       </c>
       <c r="G310" t="n">
         <v>3219.49</v>
@@ -9187,7 +9187,7 @@
         <v>47</v>
       </c>
       <c r="F313" t="n">
-        <v>8239</v>
+        <v>8238</v>
       </c>
       <c r="G313" t="n">
         <v>3033.06</v>
@@ -9246,10 +9246,10 @@
         <v>45782</v>
       </c>
       <c r="G315" t="n">
-        <v>18930.45</v>
+        <v>20299.09</v>
       </c>
       <c r="H315" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="316">
@@ -9349,19 +9349,19 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>9345.82</v>
+        <v>9343.33</v>
       </c>
       <c r="E319" t="n">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F319" t="n">
-        <v>134463</v>
+        <v>134457</v>
       </c>
       <c r="G319" t="n">
-        <v>32064.47</v>
+        <v>34309.39</v>
       </c>
       <c r="H319" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="320">
@@ -9439,7 +9439,7 @@
         <v>447</v>
       </c>
       <c r="F322" t="n">
-        <v>155594</v>
+        <v>155593</v>
       </c>
       <c r="G322" t="n">
         <v>5122.88</v>
@@ -9523,7 +9523,7 @@
         <v>26</v>
       </c>
       <c r="F325" t="n">
-        <v>6427</v>
+        <v>6426</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>201.41</v>
+        <v>193.41</v>
       </c>
       <c r="E326" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F326" t="n">
-        <v>4853</v>
+        <v>4851</v>
       </c>
       <c r="G326" t="n">
         <v>4489.83</v>
@@ -9719,7 +9719,7 @@
         <v>68</v>
       </c>
       <c r="F332" t="n">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="G332" t="n">
         <v>13598.29</v>
@@ -10111,7 +10111,7 @@
         <v>61</v>
       </c>
       <c r="F346" t="n">
-        <v>8200</v>
+        <v>8198</v>
       </c>
       <c r="G346" t="n">
         <v>0</v>
@@ -10251,7 +10251,7 @@
         <v>693</v>
       </c>
       <c r="F351" t="n">
-        <v>65929</v>
+        <v>65928</v>
       </c>
       <c r="G351" t="n">
         <v>21120.8</v>
@@ -10335,7 +10335,7 @@
         <v>9</v>
       </c>
       <c r="F354" t="n">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="G354" t="n">
         <v>0</v>
@@ -10615,7 +10615,7 @@
         <v>20</v>
       </c>
       <c r="F364" t="n">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="G364" t="n">
         <v>677.12</v>
@@ -11259,7 +11259,7 @@
         <v>6</v>
       </c>
       <c r="F387" t="n">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="G387" t="n">
         <v>0</v>
@@ -11287,7 +11287,7 @@
         <v>12</v>
       </c>
       <c r="F388" t="n">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="G388" t="n">
         <v>0</v>
@@ -11623,7 +11623,7 @@
         <v>19</v>
       </c>
       <c r="F400" t="n">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="G400" t="n">
         <v>0</v>
@@ -12015,7 +12015,7 @@
         <v>33</v>
       </c>
       <c r="F414" t="n">
-        <v>6253</v>
+        <v>6252</v>
       </c>
       <c r="G414" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>124</v>
       </c>
       <c r="F416" t="n">
-        <v>11724</v>
+        <v>11723</v>
       </c>
       <c r="G416" t="n">
         <v>17455.93</v>
@@ -12494,10 +12494,10 @@
         <v>17537</v>
       </c>
       <c r="G431" t="n">
-        <v>21522.88</v>
+        <v>1355.08</v>
       </c>
       <c r="H431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -12774,10 +12774,10 @@
         <v>30984</v>
       </c>
       <c r="G441" t="n">
-        <v>7454.23</v>
+        <v>9316.939999999999</v>
       </c>
       <c r="H441" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="442">
@@ -12802,10 +12802,10 @@
         <v>50828</v>
       </c>
       <c r="G442" t="n">
-        <v>25844.09</v>
+        <v>31816.98</v>
       </c>
       <c r="H442" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="443">
@@ -12849,13 +12849,13 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>773.88</v>
+        <v>765.88</v>
       </c>
       <c r="E444" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F444" t="n">
-        <v>10911</v>
+        <v>10910</v>
       </c>
       <c r="G444" t="n">
         <v>12173.34</v>
@@ -12942,10 +12942,10 @@
         <v>25906</v>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
+        <v>11438.98</v>
       </c>
       <c r="H447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -13275,7 +13275,7 @@
         <v>12</v>
       </c>
       <c r="F459" t="n">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="G459" t="n">
         <v>0</v>
@@ -13415,7 +13415,7 @@
         <v>2</v>
       </c>
       <c r="F464" t="n">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G464" t="n">
         <v>0</v>
@@ -13443,7 +13443,7 @@
         <v>19</v>
       </c>
       <c r="F465" t="n">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="G465" t="n">
         <v>0</v>
@@ -13471,7 +13471,7 @@
         <v>103</v>
       </c>
       <c r="F466" t="n">
-        <v>20919</v>
+        <v>20918</v>
       </c>
       <c r="G466" t="n">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>21</v>
       </c>
       <c r="F468" t="n">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G468" t="n">
         <v>0</v>
@@ -13555,7 +13555,7 @@
         <v>11</v>
       </c>
       <c r="F469" t="n">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="G469" t="n">
         <v>0</v>
@@ -13617,7 +13617,7 @@
         <v>11711.71</v>
       </c>
       <c r="H471" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472">
@@ -13695,13 +13695,13 @@
         <v>136</v>
       </c>
       <c r="F474" t="n">
-        <v>23527</v>
+        <v>23526</v>
       </c>
       <c r="G474" t="n">
-        <v>5501.7</v>
+        <v>6051.7</v>
       </c>
       <c r="H474" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="475">
@@ -13863,7 +13863,7 @@
         <v>184</v>
       </c>
       <c r="F480" t="n">
-        <v>39997</v>
+        <v>39994</v>
       </c>
       <c r="G480" t="n">
         <v>15161.97</v>
@@ -13891,7 +13891,7 @@
         <v>44</v>
       </c>
       <c r="F481" t="n">
-        <v>12864</v>
+        <v>12863</v>
       </c>
       <c r="G481" t="n">
         <v>0</v>
@@ -13975,7 +13975,7 @@
         <v>133</v>
       </c>
       <c r="F484" t="n">
-        <v>36715</v>
+        <v>36710</v>
       </c>
       <c r="G484" t="n">
         <v>8748.309999999999</v>
@@ -14031,13 +14031,13 @@
         <v>43</v>
       </c>
       <c r="F486" t="n">
-        <v>10689</v>
+        <v>10688</v>
       </c>
       <c r="G486" t="n">
-        <v>1694.07</v>
+        <v>3405.09</v>
       </c>
       <c r="H486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -14115,7 +14115,7 @@
         <v>15</v>
       </c>
       <c r="F489" t="n">
-        <v>4620</v>
+        <v>4619</v>
       </c>
       <c r="G489" t="n">
         <v>2456.78</v>
@@ -14227,7 +14227,7 @@
         <v>58</v>
       </c>
       <c r="F493" t="n">
-        <v>14348</v>
+        <v>14347</v>
       </c>
       <c r="G493" t="n">
         <v>0</v>
@@ -14255,7 +14255,7 @@
         <v>35</v>
       </c>
       <c r="F494" t="n">
-        <v>7424</v>
+        <v>7423</v>
       </c>
       <c r="G494" t="n">
         <v>1694.07</v>
@@ -14283,7 +14283,7 @@
         <v>59</v>
       </c>
       <c r="F495" t="n">
-        <v>9285</v>
+        <v>9284</v>
       </c>
       <c r="G495" t="n">
         <v>1694.07</v>
@@ -14339,7 +14339,7 @@
         <v>13</v>
       </c>
       <c r="F497" t="n">
-        <v>4756</v>
+        <v>4755</v>
       </c>
       <c r="G497" t="n">
         <v>0</v>
@@ -14395,7 +14395,7 @@
         <v>28</v>
       </c>
       <c r="F499" t="n">
-        <v>7586</v>
+        <v>7585</v>
       </c>
       <c r="G499" t="n">
         <v>0</v>
@@ -14423,7 +14423,7 @@
         <v>156</v>
       </c>
       <c r="F500" t="n">
-        <v>34080</v>
+        <v>34079</v>
       </c>
       <c r="G500" t="n">
         <v>10333.91</v>
@@ -14451,13 +14451,13 @@
         <v>45</v>
       </c>
       <c r="F501" t="n">
-        <v>14830</v>
+        <v>14829</v>
       </c>
       <c r="G501" t="n">
-        <v>1778.81</v>
+        <v>3854.23</v>
       </c>
       <c r="H501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -14669,13 +14669,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4303.29</v>
+        <v>4294.85</v>
       </c>
       <c r="E6" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F6" t="n">
-        <v>80380</v>
+        <v>80374</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -14697,19 +14697,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2030.41</v>
+        <v>2027.15</v>
       </c>
       <c r="E7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F7" t="n">
         <v>69081</v>
       </c>
       <c r="G7" t="n">
-        <v>13552.54</v>
+        <v>16940.68</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -14731,7 +14731,7 @@
         <v>698</v>
       </c>
       <c r="F8" t="n">
-        <v>195962</v>
+        <v>195960</v>
       </c>
       <c r="G8" t="n">
         <v>5802.55</v>
@@ -14899,13 +14899,13 @@
         <v>640</v>
       </c>
       <c r="F14" t="n">
-        <v>170599</v>
+        <v>170594</v>
       </c>
       <c r="G14" t="n">
-        <v>39705.09</v>
+        <v>41399.16</v>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -14955,7 +14955,7 @@
         <v>215</v>
       </c>
       <c r="F16" t="n">
-        <v>79023</v>
+        <v>79021</v>
       </c>
       <c r="G16" t="n">
         <v>10843.24</v>
@@ -15005,10 +15005,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>821.6</v>
+        <v>820.5699999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" t="n">
         <v>49510</v>
@@ -15291,7 +15291,7 @@
         <v>1991</v>
       </c>
       <c r="F28" t="n">
-        <v>565025</v>
+        <v>565018</v>
       </c>
       <c r="G28" t="n">
         <v>21183.9</v>
@@ -15481,13 +15481,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3686.17</v>
+        <v>3685.16</v>
       </c>
       <c r="E35" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F35" t="n">
-        <v>152549</v>
+        <v>152543</v>
       </c>
       <c r="G35" t="n">
         <v>13654.69</v>
@@ -15543,13 +15543,13 @@
         <v>148</v>
       </c>
       <c r="F37" t="n">
-        <v>26810</v>
+        <v>26804</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>7033.05</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -15621,19 +15621,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6950.3</v>
+        <v>6946.16</v>
       </c>
       <c r="E40" t="n">
-        <v>4059</v>
+        <v>4055</v>
       </c>
       <c r="F40" t="n">
-        <v>1004717</v>
+        <v>1004701</v>
       </c>
       <c r="G40" t="n">
-        <v>20250.85</v>
+        <v>34316.95</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -15767,7 +15767,7 @@
         <v>504</v>
       </c>
       <c r="F45" t="n">
-        <v>148849</v>
+        <v>148841</v>
       </c>
       <c r="G45" t="n">
         <v>27574.63</v>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38236</v>
+        <v>38235</v>
       </c>
       <c r="E11" t="n">
         <v>394</v>
@@ -16184,7 +16184,7 @@
         <v>6988.744211349059</v>
       </c>
       <c r="G11" t="n">
-        <v>8979.68</v>
+        <v>10679.37142362812</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -16217,10 +16217,10 @@
         <v>2241.855788650941</v>
       </c>
       <c r="G12" t="n">
-        <v>2880.51</v>
+        <v>3425.738576371879</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>713.6148785311477</v>
+        <v>711.8881959737676</v>
       </c>
       <c r="G14" t="n">
         <v>6777.96</v>
@@ -16313,7 +16313,7 @@
         <v>104</v>
       </c>
       <c r="F15" t="n">
-        <v>838.3518736577879</v>
+        <v>836.3233739715545</v>
       </c>
       <c r="G15" t="n">
         <v>7962.719999999999</v>
@@ -16349,7 +16349,7 @@
         <v>1315.01219351602</v>
       </c>
       <c r="G16" t="n">
-        <v>1105.94</v>
+        <v>2069.735454001105</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -16415,10 +16415,10 @@
         <v>3828.11780648398</v>
       </c>
       <c r="G18" t="n">
-        <v>3219.49</v>
+        <v>6025.184545998894</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -16442,10 +16442,10 @@
         <v>20809</v>
       </c>
       <c r="E19" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F19" t="n">
-        <v>927.7532478110641</v>
+        <v>925.5084300546778</v>
       </c>
       <c r="G19" t="n">
         <v>8811.860000000001</v>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week23.xlsx
@@ -15647,7 +15647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15739,23 +15739,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10278</v>
+        <v>9349</v>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>1719.543333333333</v>
+        <v>1564.135148498263</v>
       </c>
       <c r="G3" t="n">
-        <v>6199.153333333333</v>
+        <v>5638.88878612936</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -15772,23 +15772,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10278</v>
+        <v>4151</v>
       </c>
       <c r="E4" t="n">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>1719.543333333333</v>
+        <v>694.5199540278804</v>
       </c>
       <c r="G4" t="n">
-        <v>6199.153333333333</v>
+        <v>2503.825059024459</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -15809,19 +15809,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10278</v>
+        <v>6150</v>
       </c>
       <c r="E5" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
-        <v>1719.543333333333</v>
+        <v>1028.944387175992</v>
       </c>
       <c r="G5" t="n">
-        <v>6199.153333333333</v>
+        <v>3709.4639628603</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -15833,28 +15833,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72753</v>
+        <v>11184</v>
       </c>
       <c r="E6" t="n">
-        <v>514</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>5112.01</v>
+        <v>1871.030510297865</v>
       </c>
       <c r="G6" t="n">
-        <v>8133.9</v>
+        <v>6745.282191985881</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -15866,28 +15866,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7299</v>
+        <v>72753</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>514</v>
       </c>
       <c r="F7" t="n">
-        <v>804.73</v>
+        <v>5112.01</v>
       </c>
       <c r="G7" t="n">
-        <v>8811.860000000001</v>
+        <v>8133.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15908,19 +15908,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>7299</v>
       </c>
       <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>804.73</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8811.860000000001</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -15932,28 +15932,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18462</v>
+        <v>377</v>
       </c>
       <c r="E9" t="n">
-        <v>227</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>2243.35</v>
+        <v>9.48</v>
       </c>
       <c r="G9" t="n">
-        <v>5931.36</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -15965,28 +15965,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13451</v>
+        <v>18462</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="F10" t="n">
-        <v>2637.876666666667</v>
+        <v>2243.35</v>
       </c>
       <c r="G10" t="n">
-        <v>4701.703333333334</v>
+        <v>5931.36</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -16003,23 +16003,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13451</v>
+        <v>30553</v>
       </c>
       <c r="E11" t="n">
-        <v>146</v>
+        <v>331</v>
       </c>
       <c r="F11" t="n">
-        <v>2637.876666666667</v>
+        <v>5991.629563978317</v>
       </c>
       <c r="G11" t="n">
-        <v>4701.703333333334</v>
+        <v>10679.37142362812</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -16036,20 +16036,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13451</v>
+        <v>9801</v>
       </c>
       <c r="E12" t="n">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
-        <v>2637.876666666667</v>
+        <v>1922.000436021683</v>
       </c>
       <c r="G12" t="n">
-        <v>4701.703333333334</v>
+        <v>3425.738576371879</v>
       </c>
       <c r="H12" t="n">
         <v>2</v>
@@ -16073,19 +16073,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5643</v>
+        <v>49883</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="F13" t="n">
-        <v>411.0124137931034</v>
+        <v>2108.43</v>
       </c>
       <c r="G13" t="n">
-        <v>1968.206206896552</v>
+        <v>4489.84</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -16102,20 +16102,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5643</v>
+        <v>8591</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>411.0124137931034</v>
+        <v>378.5995468359754</v>
       </c>
       <c r="G14" t="n">
-        <v>1968.206206896552</v>
+        <v>3388.98</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -16135,23 +16135,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5643</v>
+        <v>20185</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="F15" t="n">
-        <v>411.0124137931034</v>
+        <v>889.5544333639497</v>
       </c>
       <c r="G15" t="n">
-        <v>1968.206206896552</v>
+        <v>7962.72</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -16168,20 +16168,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5643</v>
+        <v>6119</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>411.0124137931034</v>
+        <v>1175.969085339492</v>
       </c>
       <c r="G16" t="n">
-        <v>1968.206206896552</v>
+        <v>2069.735454001105</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -16201,23 +16201,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5643</v>
+        <v>35719</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="F17" t="n">
-        <v>411.0124137931034</v>
+        <v>2729.409728493959</v>
       </c>
       <c r="G17" t="n">
-        <v>1968.206206896552</v>
+        <v>22441.60629628202</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -16234,23 +16234,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5643</v>
+        <v>17811</v>
       </c>
       <c r="E18" t="n">
-        <v>35</v>
+        <v>214</v>
       </c>
       <c r="F18" t="n">
-        <v>411.0124137931034</v>
+        <v>3423.350914660507</v>
       </c>
       <c r="G18" t="n">
-        <v>1968.206206896552</v>
+        <v>6025.184545998894</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -16267,23 +16267,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5643</v>
+        <v>22338</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="F19" t="n">
-        <v>411.0124137931034</v>
+        <v>984.4160198000751</v>
       </c>
       <c r="G19" t="n">
-        <v>1968.206206896552</v>
+        <v>8811.860000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -16300,718 +16300,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5643</v>
+        <v>3005</v>
       </c>
       <c r="E20" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>411.0124137931034</v>
+        <v>229.6302715060409</v>
       </c>
       <c r="G20" t="n">
-        <v>1968.206206896552</v>
+        <v>1888.053703717984</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>B0BLJVJ2GN</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E21" t="n">
-        <v>35</v>
-      </c>
-      <c r="F21" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>B0BLK8DNPD</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E22" t="n">
-        <v>35</v>
-      </c>
-      <c r="F22" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B0BPLZ5CGV</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E23" t="n">
-        <v>35</v>
-      </c>
-      <c r="F23" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>B0C4YTNJG7</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E24" t="n">
-        <v>35</v>
-      </c>
-      <c r="F24" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0C539RBGL</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E25" t="n">
-        <v>35</v>
-      </c>
-      <c r="F25" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>B0CF5R3V95</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E26" t="n">
-        <v>35</v>
-      </c>
-      <c r="F26" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>B0CF5RRTDJ</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E27" t="n">
-        <v>35</v>
-      </c>
-      <c r="F27" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>B0CF5TCQKL</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E28" t="n">
-        <v>35</v>
-      </c>
-      <c r="F28" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>B0CH4RT4P8</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E29" t="n">
-        <v>35</v>
-      </c>
-      <c r="F29" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>B0CKHVHVQ1</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E30" t="n">
-        <v>35</v>
-      </c>
-      <c r="F30" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>B0CM6NTWBP</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E31" t="n">
-        <v>35</v>
-      </c>
-      <c r="F31" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>B0D3M1B4Z8</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E32" t="n">
-        <v>35</v>
-      </c>
-      <c r="F32" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>B0DFMLS8JG</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E33" t="n">
-        <v>35</v>
-      </c>
-      <c r="F33" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>B0DFMMTWLY</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E34" t="n">
-        <v>35</v>
-      </c>
-      <c r="F34" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>B0DFMNGFTD</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E35" t="n">
-        <v>35</v>
-      </c>
-      <c r="F35" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>B0DT6T6N6B</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E36" t="n">
-        <v>35</v>
-      </c>
-      <c r="F36" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>B0FF9R3GKK</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E37" t="n">
-        <v>35</v>
-      </c>
-      <c r="F37" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>B0G2C2RCXN</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E38" t="n">
-        <v>35</v>
-      </c>
-      <c r="F38" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>B0G3Q517Y2</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E39" t="n">
-        <v>35</v>
-      </c>
-      <c r="F39" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>B0G3Q59X8C</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E40" t="n">
-        <v>35</v>
-      </c>
-      <c r="F40" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0G4DNF8RZ</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>5643</v>
-      </c>
-      <c r="E41" t="n">
-        <v>35</v>
-      </c>
-      <c r="F41" t="n">
-        <v>411.0124137931034</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1968.206206896552</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>
